--- a/docs/PPB_Touch_API_Contact_List.xlsx
+++ b/docs/PPB_Touch_API_Contact_List.xlsx
@@ -623,7 +623,7 @@
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       <c r="H42" s="3" t="inlineStr"/>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
       <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
       <c r="H49" s="3" t="inlineStr"/>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       <c r="H50" s="3" t="inlineStr"/>
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       <c r="H52" s="3" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
       <c r="H63" s="3" t="inlineStr"/>
       <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
       <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       <c r="H65" s="3" t="inlineStr"/>
       <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr"/>
       <c r="J71" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
       <c r="H72" s="3" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr"/>
       <c r="J72" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       <c r="H73" s="3" t="inlineStr"/>
       <c r="I73" s="3" t="inlineStr"/>
       <c r="J73" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
       <c r="H74" s="3" t="inlineStr"/>
       <c r="I74" s="3" t="inlineStr"/>
       <c r="J74" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
       <c r="H75" s="3" t="inlineStr"/>
       <c r="I75" s="3" t="inlineStr"/>
       <c r="J75" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
       <c r="H76" s="3" t="inlineStr"/>
       <c r="I76" s="3" t="inlineStr"/>
       <c r="J76" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
       <c r="H80" s="3" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr"/>
       <c r="J80" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       <c r="H82" s="3" t="inlineStr"/>
       <c r="I82" s="3" t="inlineStr"/>
       <c r="J82" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
       <c r="H83" s="3" t="inlineStr"/>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       <c r="H84" s="3" t="inlineStr"/>
       <c r="I84" s="3" t="inlineStr"/>
       <c r="J84" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
       <c r="H85" s="3" t="inlineStr"/>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       <c r="H86" s="3" t="inlineStr"/>
       <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       <c r="H88" s="3" t="inlineStr"/>
       <c r="I88" s="3" t="inlineStr"/>
       <c r="J88" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
       <c r="H90" s="3" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       <c r="H92" s="3" t="inlineStr"/>
       <c r="I92" s="3" t="inlineStr"/>
       <c r="J92" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="J94" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       <c r="H95" s="3" t="inlineStr"/>
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
       <c r="H96" s="3" t="inlineStr"/>
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
       <c r="H97" s="3" t="inlineStr"/>
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="J105" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="J109" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="J110" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="J111" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="J112" s="3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
